--- a/02_DIA_inicio_2026_analisis_assets/rbd_9593_escuela-basica-educadores-de-chile_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9593_escuela-basica-educadores-de-chile_nt1_rubricas.xlsx
@@ -1788,13 +1788,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDCE31AA-963A-4C9D-B9D4-675DD6A8954C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A77C753-71E3-48C4-9EB5-7A3102480EE6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64F53D8B-E62A-42E5-86A2-B97CD7CEB6D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5425F38-92D9-4151-8B73-4E36BFE4B93C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19D5CFC5-8DFA-4AC9-8391-AE87E7273BCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34800FC-5D97-4F9B-94EF-DFD51DF6C153}"/>
 </file>